--- a/Day 6 (3).xlsx
+++ b/Day 6 (3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Saumil Data Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E57120-47EF-41E9-B895-D122B779924B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A66EEA-9E05-4A2D-BB9B-D946EC0FF47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{AC3146FC-E3A9-4E58-838B-57C895522AD9}"/>
   </bookViews>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="X3" s="15">
         <f ca="1">NOW()</f>
-        <v>46124.686947222224</v>
+        <v>46124.769132986112</v>
       </c>
       <c r="Y3" s="11" t="e">
         <f>EDATE(G3,5)</f>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="J2" s="23">
         <f ca="1">NOW()</f>
-        <v>46124.686947222224</v>
+        <v>46124.769132986112</v>
       </c>
       <c r="K2" s="25">
         <f>NETWORKDAYS.INTL(D2,C2,11,2)</f>
